--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -729,7 +729,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -810,7 +810,7 @@
     <t>Codes for high level media categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -930,7 +930,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -979,7 +979,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1055,7 +1055,7 @@
     <t>Media.operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-practitioner) &lt;&lt;referenced&gt;&gt;
+    <t xml:space="preserve">Reference(http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-practitioner|http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-patient|http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-relatedperson) &lt;&lt;referenced&gt;&gt;
 </t>
   </si>
   <si>
@@ -1095,7 +1095,7 @@
     <t>The reason for the media.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1287,7 +1287,7 @@
     <t>Media.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1690,7 +1690,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="36.890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.98046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-media.xlsx
+++ b/fhir/StructureDefinition-ehealth-media.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
